--- a/polymercanon/Paper-Results/Excel/Same polymer many notations/Same polymer many notations.xlsx
+++ b/polymercanon/Paper-Results/Excel/Same polymer many notations/Same polymer many notations.xlsx
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
+          <t>[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}OCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
         </is>
       </c>
     </row>
